--- a/data/xlsx/basis--technical-sales-specialist-it-sector.xlsx
+++ b/data/xlsx/basis--technical-sales-specialist-it-sector.xlsx
@@ -648,7 +648,9 @@
       <c r="C16" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>6</v>
       </c>
@@ -670,7 +672,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
